--- a/output/pdf_financials_xlsx/FSV.xlsx
+++ b/output/pdf_financials_xlsx/FSV.xlsx
@@ -2544,37 +2544,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>169.863</v>
+        <v>20.715</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>164.674</v>
+        <v>21.749</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>226.9</v>
+        <v>25.853</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>227.721</v>
+        <v>31.367</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>296.293</v>
+        <v>37.739</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>448.394</v>
+        <v>41.457</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>632.889</v>
+        <v>50.596</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>725.431</v>
+        <v>50.347</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1169.147</v>
+        <v>56.888</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1327.83</v>
+        <v>79.093</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1344.635</v>
+        <v>105.229</v>
       </c>
     </row>
     <row r="49">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/output/pdf_financials_xlsx/FSV.xlsx
+++ b/output/pdf_financials_xlsx/FSV.xlsx
@@ -2544,37 +2544,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>20.715</v>
+        <v>169.863</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>21.749</v>
+        <v>164.674</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.853</v>
+        <v>226.9</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.367</v>
+        <v>227.721</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>37.739</v>
+        <v>296.293</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>41.457</v>
+        <v>448.394</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>50.596</v>
+        <v>632.889</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>50.347</v>
+        <v>725.431</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>56.888</v>
+        <v>1169.147</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>79.093</v>
+        <v>1327.83</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>105.229</v>
+        <v>1344.635</v>
       </c>
     </row>
     <row r="49">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/output/pdf_financials_xlsx/FSV.xlsx
+++ b/output/pdf_financials_xlsx/FSV.xlsx
@@ -1687,40 +1687,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>39.316</v>
+        <v>23.606</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>26.474</v>
+        <v>8.744</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>28.984</v>
+        <v>10.148</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>36.969</v>
+        <v>14.195</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>42.049</v>
+        <v>14.354</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>52.772</v>
+        <v>17.515</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>79.557</v>
+        <v>38.698</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>98.965</v>
+        <v>43.891</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>110.14</v>
+        <v>48.725</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>127.934</v>
+        <v>54.238</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>165.269</v>
+        <v>72.396</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>185.209</v>
+        <v>77.238</v>
       </c>
     </row>
     <row r="29">
@@ -1730,40 +1730,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>63.553</v>
+        <v>47.843</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>64.908</v>
+        <v>47.178</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>90.59399999999999</v>
+        <v>71.758</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>118.599</v>
+        <v>95.825</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>138.664</v>
+        <v>110.969</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>167.974</v>
+        <v>132.717</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-120.927</v>
+        <v>-161.786</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>307.97</v>
+        <v>252.896</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>304.121</v>
+        <v>242.706</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>331.272</v>
+        <v>257.576</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>423.167</v>
+        <v>330.294</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>451.721</v>
+        <v>343.75</v>
       </c>
     </row>
     <row r="30">
@@ -1773,40 +1773,40 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.122126565499808</v>
+        <v>4.608765931949828</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5.733912130897295</v>
+        <v>4.167660481165228</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>7.166810249692068</v>
+        <v>5.676711149716354</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>7.997833957902446</v>
+        <v>6.462048069680199</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.019752103924105</v>
+        <v>6.417987878759837</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.69667864888611</v>
+        <v>6.871284247825364</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-5.023116128951862</v>
+        <v>-6.720334301178445</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.478706535281459</v>
+        <v>7.783637912610124</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>8.118910736858403</v>
+        <v>6.479356405180687</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>7.642596183039155</v>
+        <v>5.942395839197074</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>8.111473991996004</v>
+        <v>6.331238472547075</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>8.216844020009095</v>
+        <v>6.252842201000456</v>
       </c>
     </row>
     <row r="31">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">
@@ -29360,7 +29360,11 @@
           <t>Accelerated amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E321" s="5" t="n">
         <v>11.184</v>
       </c>

--- a/output/pdf_financials_xlsx/FSV.xlsx
+++ b/output/pdf_financials_xlsx/FSV.xlsx
@@ -5144,40 +5144,40 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-5.243</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-3.327</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-1.045</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-1.793</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-3.656</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-6.152</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-1.033</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-8.590999999999999</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-4.84</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-15.026</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-25.484</v>
       </c>
     </row>
     <row r="104">
@@ -5273,40 +5273,40 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-6.864</v>
+        <v>-12.107</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.308</v>
+        <v>-2.019</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>16.748</v>
+        <v>15.703</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-12.339</v>
+        <v>-14.132</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-13.104</v>
+        <v>-16.76</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-33.667</v>
+        <v>-39.819</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-16.417</v>
+        <v>-17.45</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-100.482</v>
+        <v>-109.073</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-138.487</v>
+        <v>-138.221</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-62.735</v>
+        <v>-67.575</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-45.408</v>
+        <v>-60.434</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>53.913</v>
+        <v>28.429</v>
       </c>
     </row>
     <row r="107">
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-8.997999999999999</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -6013,22 +6013,22 @@
         <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>101.16</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>61.063</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>103.914</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>624.052</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>130.48</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>150.156</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>587.847</v>
@@ -6099,22 +6099,22 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-51.775</v>
+        <v>49.385</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-43.641</v>
+        <v>17.422</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-41.626</v>
+        <v>62.288</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-194.193</v>
+        <v>429.859</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-68.422</v>
+        <v>62.058</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-70</v>
+        <v>80.15600000000001</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>446.847</v>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-1.092</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0</v>
+        <v>-2.468</v>
       </c>
       <c r="K128" s="3" t="n">
         <v>0</v>
@@ -21444,7 +21444,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E205" s="5" t="n">
         <v>-5.243</v>
       </c>
@@ -23294,7 +23298,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -23358,7 +23366,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -23880,7 +23892,11 @@
           <t>Repurchases of Common Shares</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27750,7 +27766,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -28046,7 +28066,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
